--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,6 +5794,3067 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120459839</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>514180</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7128054</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120458931</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>514084</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7128053</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120458347</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91146</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>760</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>513938</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7128279</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120457729</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>514077</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7128136</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120460472</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>514351</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7127962</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120460105</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>514241</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7127904</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120457160</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>514165</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7128093</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120457678</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>514096</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7128129</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120459749</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>514168</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7128051</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120458603</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>514073</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7128124</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120457474</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>514114</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7128116</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120457063</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>514185</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7128134</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120458790</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>514077</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7128067</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack med nyligen intorkad kåda</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120457746</v>
+      </c>
+      <c r="B59" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>514069</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7128147</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120460533</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>514358</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7127980</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120457642</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>514115</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7128095</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120459988</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>514236</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7127956</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120456991</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>514191</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7128149</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120460607</v>
+      </c>
+      <c r="B64" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>514397</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7127995</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120458528</v>
+      </c>
+      <c r="B65" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>514056</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7128156</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120457216</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>514115</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7128119</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120461048</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>514341</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7127864</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120458497</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>514044</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7128164</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120456942</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>514195</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7128135</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120457567</v>
+      </c>
+      <c r="B70" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>514117</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7128094</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120459113</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>514080</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7128047</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120458309</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>513941</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7128278</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120457132</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>514162</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7128103</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120458240</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Strömsund, Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>513929</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7128250</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -5796,10 +5796,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120459839</v>
+        <v>120458528</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5808,25 +5808,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514180</v>
+        <v>514056</v>
       </c>
       <c r="R46" t="n">
-        <v>7128054</v>
+        <v>7128156</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5872,11 +5872,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5903,10 +5898,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120458931</v>
+        <v>120458309</v>
       </c>
       <c r="B47" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5915,45 +5910,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514084</v>
+        <v>513941</v>
       </c>
       <c r="R47" t="n">
-        <v>7128053</v>
+        <v>7128278</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6009,10 +6000,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120458347</v>
+        <v>120458931</v>
       </c>
       <c r="B48" t="n">
-        <v>91146</v>
+        <v>57431</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6021,41 +6012,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>760</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513938</v>
+        <v>514084</v>
       </c>
       <c r="R48" t="n">
-        <v>7128279</v>
+        <v>7128053</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6111,10 +6106,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120457729</v>
+        <v>120457567</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6127,39 +6122,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514077</v>
+        <v>514117</v>
       </c>
       <c r="R49" t="n">
-        <v>7128136</v>
+        <v>7128094</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6192,11 +6182,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6223,10 +6208,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120460472</v>
+        <v>120459839</v>
       </c>
       <c r="B50" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6235,25 +6220,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6263,13 +6248,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514351</v>
+        <v>514180</v>
       </c>
       <c r="R50" t="n">
-        <v>7127962</v>
+        <v>7128054</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6299,6 +6284,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6325,10 +6315,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120460105</v>
+        <v>120459749</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6341,21 +6331,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6365,10 +6355,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514241</v>
+        <v>514168</v>
       </c>
       <c r="R51" t="n">
-        <v>7127904</v>
+        <v>7128051</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6401,11 +6391,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6432,10 +6417,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120457160</v>
+        <v>120457474</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,37 +6433,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514165</v>
+        <v>514114</v>
       </c>
       <c r="R52" t="n">
-        <v>7128093</v>
+        <v>7128116</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6534,7 +6524,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120457678</v>
+        <v>120460105</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6574,13 +6564,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514096</v>
+        <v>514241</v>
       </c>
       <c r="R53" t="n">
-        <v>7128129</v>
+        <v>7127904</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6641,10 +6631,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120459749</v>
+        <v>120458347</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>91146</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6653,25 +6643,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6681,10 +6671,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514168</v>
+        <v>513938</v>
       </c>
       <c r="R54" t="n">
-        <v>7128051</v>
+        <v>7128279</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6743,10 +6733,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120458603</v>
+        <v>120460607</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6755,46 +6745,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514073</v>
+        <v>514397</v>
       </c>
       <c r="R55" t="n">
-        <v>7128124</v>
+        <v>7127995</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6824,11 +6809,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6855,10 +6835,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120457474</v>
+        <v>120457729</v>
       </c>
       <c r="B56" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6871,27 +6851,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6900,13 +6880,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514114</v>
+        <v>514077</v>
       </c>
       <c r="R56" t="n">
-        <v>7128116</v>
+        <v>7128136</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6936,6 +6916,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6962,10 +6947,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120457063</v>
+        <v>120460472</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6974,43 +6959,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>514185</v>
+        <v>514351</v>
       </c>
       <c r="R57" t="n">
-        <v>7128134</v>
+        <v>7127962</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7043,11 +7023,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7074,10 +7049,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120458790</v>
+        <v>120457746</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7090,42 +7065,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>514077</v>
+        <v>514069</v>
       </c>
       <c r="R58" t="n">
-        <v>7128067</v>
+        <v>7128147</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7155,11 +7125,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack med nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7186,10 +7151,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120457746</v>
+        <v>120457678</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7202,21 +7167,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7226,10 +7191,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>514069</v>
+        <v>514096</v>
       </c>
       <c r="R59" t="n">
-        <v>7128147</v>
+        <v>7128129</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7262,6 +7227,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7288,7 +7258,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120460533</v>
+        <v>120458240</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -7322,21 +7292,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>514358</v>
+        <v>513929</v>
       </c>
       <c r="R60" t="n">
-        <v>7127980</v>
+        <v>7128250</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7373,7 +7338,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7400,10 +7365,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120457642</v>
+        <v>120456991</v>
       </c>
       <c r="B61" t="n">
-        <v>90972</v>
+        <v>78278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7416,16 +7381,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6040186</v>
+        <v>6446</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7435,13 +7405,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>514115</v>
+        <v>514191</v>
       </c>
       <c r="R61" t="n">
-        <v>7128095</v>
+        <v>7128149</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7599,10 +7569,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120456991</v>
+        <v>120460533</v>
       </c>
       <c r="B63" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7615,37 +7585,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>514191</v>
+        <v>514358</v>
       </c>
       <c r="R63" t="n">
-        <v>7128149</v>
+        <v>7127980</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7675,6 +7650,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7701,10 +7681,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120460607</v>
+        <v>120457216</v>
       </c>
       <c r="B64" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,25 +7693,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7741,13 +7721,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>514397</v>
+        <v>514115</v>
       </c>
       <c r="R64" t="n">
-        <v>7127995</v>
+        <v>7128119</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7803,10 +7783,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120458528</v>
+        <v>120459113</v>
       </c>
       <c r="B65" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,25 +7795,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7843,13 +7823,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>514056</v>
+        <v>514080</v>
       </c>
       <c r="R65" t="n">
-        <v>7128156</v>
+        <v>7128047</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7879,6 +7859,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7905,10 +7890,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120457216</v>
+        <v>120458603</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7921,34 +7906,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>514115</v>
+        <v>514073</v>
       </c>
       <c r="R66" t="n">
-        <v>7128119</v>
+        <v>7128124</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7981,6 +7971,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8007,7 +8002,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120461048</v>
+        <v>120457063</v>
       </c>
       <c r="B67" t="n">
         <v>57320</v>
@@ -8041,19 +8036,24 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>514341</v>
+        <v>514185</v>
       </c>
       <c r="R67" t="n">
-        <v>7127864</v>
+        <v>7128134</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120458497</v>
+        <v>120457642</v>
       </c>
       <c r="B68" t="n">
-        <v>57431</v>
+        <v>90972</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8126,50 +8126,36 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>514044</v>
+        <v>514115</v>
       </c>
       <c r="R68" t="n">
-        <v>7128164</v>
+        <v>7128095</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8225,7 +8211,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120456942</v>
+        <v>120458790</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -8259,16 +8245,21 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514195</v>
+        <v>514077</v>
       </c>
       <c r="R69" t="n">
-        <v>7128135</v>
+        <v>7128067</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8305,7 +8296,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack med nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8332,10 +8323,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120457567</v>
+        <v>120458497</v>
       </c>
       <c r="B70" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8344,41 +8335,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>514117</v>
+        <v>514044</v>
       </c>
       <c r="R70" t="n">
-        <v>7128094</v>
+        <v>7128164</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120459113</v>
+        <v>120457132</v>
       </c>
       <c r="B71" t="n">
         <v>57320</v>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>514080</v>
+        <v>514162</v>
       </c>
       <c r="R71" t="n">
-        <v>7128047</v>
+        <v>7128103</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120458309</v>
+        <v>120456942</v>
       </c>
       <c r="B72" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8557,21 +8557,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513941</v>
+        <v>514195</v>
       </c>
       <c r="R72" t="n">
-        <v>7128278</v>
+        <v>7128135</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8617,6 +8617,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8643,7 +8648,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120457132</v>
+        <v>120461048</v>
       </c>
       <c r="B73" t="n">
         <v>57320</v>
@@ -8683,13 +8688,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>514162</v>
+        <v>514341</v>
       </c>
       <c r="R73" t="n">
-        <v>7128103</v>
+        <v>7127864</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8750,10 +8755,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120458240</v>
+        <v>120457160</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8766,21 +8771,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8790,13 +8795,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513929</v>
+        <v>514165</v>
       </c>
       <c r="R74" t="n">
-        <v>7128250</v>
+        <v>7128093</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8826,11 +8831,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -5796,10 +5796,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120458528</v>
+        <v>120457063</v>
       </c>
       <c r="B46" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5808,41 +5808,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514056</v>
+        <v>514185</v>
       </c>
       <c r="R46" t="n">
-        <v>7128156</v>
+        <v>7128134</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5872,6 +5877,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5898,10 +5908,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120458309</v>
+        <v>120460607</v>
       </c>
       <c r="B47" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5910,25 +5920,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5938,13 +5948,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513941</v>
+        <v>514397</v>
       </c>
       <c r="R47" t="n">
-        <v>7128278</v>
+        <v>7127995</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6000,10 +6010,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120458931</v>
+        <v>120458240</v>
       </c>
       <c r="B48" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6012,20 +6022,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6033,24 +6043,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514084</v>
+        <v>513929</v>
       </c>
       <c r="R48" t="n">
-        <v>7128053</v>
+        <v>7128250</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6080,6 +6086,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6106,10 +6117,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120457567</v>
+        <v>120458528</v>
       </c>
       <c r="B49" t="n">
-        <v>90598</v>
+        <v>96885</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6118,25 +6129,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6146,13 +6157,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514117</v>
+        <v>514056</v>
       </c>
       <c r="R49" t="n">
-        <v>7128094</v>
+        <v>7128156</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6208,10 +6219,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120459839</v>
+        <v>120457746</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6224,21 +6235,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6248,10 +6259,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514180</v>
+        <v>514069</v>
       </c>
       <c r="R50" t="n">
-        <v>7128054</v>
+        <v>7128147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6284,11 +6295,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6315,10 +6321,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120459749</v>
+        <v>120457216</v>
       </c>
       <c r="B51" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6331,21 +6337,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6355,10 +6361,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514168</v>
+        <v>514115</v>
       </c>
       <c r="R51" t="n">
-        <v>7128051</v>
+        <v>7128119</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6417,10 +6423,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120457474</v>
+        <v>120456942</v>
       </c>
       <c r="B52" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6433,42 +6439,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514114</v>
+        <v>514195</v>
       </c>
       <c r="R52" t="n">
-        <v>7128116</v>
+        <v>7128135</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6498,6 +6499,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6524,7 +6530,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120460105</v>
+        <v>120457132</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6564,10 +6570,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514241</v>
+        <v>514162</v>
       </c>
       <c r="R53" t="n">
-        <v>7127904</v>
+        <v>7128103</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6631,10 +6637,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120458347</v>
+        <v>120460533</v>
       </c>
       <c r="B54" t="n">
-        <v>91146</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6643,38 +6649,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513938</v>
+        <v>514358</v>
       </c>
       <c r="R54" t="n">
-        <v>7128279</v>
+        <v>7127980</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6707,6 +6718,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6733,10 +6749,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120460607</v>
+        <v>120459749</v>
       </c>
       <c r="B55" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6745,25 +6761,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6773,13 +6789,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514397</v>
+        <v>514168</v>
       </c>
       <c r="R55" t="n">
-        <v>7127995</v>
+        <v>7128051</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6835,10 +6851,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120457729</v>
+        <v>120459988</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6851,42 +6867,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514077</v>
+        <v>514236</v>
       </c>
       <c r="R56" t="n">
-        <v>7128136</v>
+        <v>7127956</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6916,11 +6927,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6947,10 +6953,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120460472</v>
+        <v>120458347</v>
       </c>
       <c r="B57" t="n">
-        <v>91879</v>
+        <v>91146</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6959,25 +6965,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>760</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6987,10 +6993,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>514351</v>
+        <v>513938</v>
       </c>
       <c r="R57" t="n">
-        <v>7127962</v>
+        <v>7128279</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7049,10 +7055,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120457746</v>
+        <v>120458931</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7061,41 +7067,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>514069</v>
+        <v>514084</v>
       </c>
       <c r="R58" t="n">
-        <v>7128147</v>
+        <v>7128053</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7258,7 +7268,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120458240</v>
+        <v>120459113</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -7298,10 +7308,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513929</v>
+        <v>514080</v>
       </c>
       <c r="R60" t="n">
-        <v>7128250</v>
+        <v>7128047</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7365,10 +7375,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120456991</v>
+        <v>120459839</v>
       </c>
       <c r="B61" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7381,21 +7391,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7405,10 +7415,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>514191</v>
+        <v>514180</v>
       </c>
       <c r="R61" t="n">
-        <v>7128149</v>
+        <v>7128054</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7441,6 +7451,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7467,10 +7482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120459988</v>
+        <v>120457729</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7483,37 +7498,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>514236</v>
+        <v>514077</v>
       </c>
       <c r="R62" t="n">
-        <v>7127956</v>
+        <v>7128136</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7543,6 +7563,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7569,10 +7594,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120460533</v>
+        <v>120457567</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7585,39 +7610,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>514358</v>
+        <v>514117</v>
       </c>
       <c r="R63" t="n">
-        <v>7127980</v>
+        <v>7128094</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7650,11 +7670,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7681,10 +7696,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120457216</v>
+        <v>120460105</v>
       </c>
       <c r="B64" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7697,21 +7712,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7721,10 +7736,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>514115</v>
+        <v>514241</v>
       </c>
       <c r="R64" t="n">
-        <v>7128119</v>
+        <v>7127904</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7757,6 +7772,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7783,7 +7803,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120459113</v>
+        <v>120458790</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7817,16 +7837,21 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>514080</v>
+        <v>514077</v>
       </c>
       <c r="R65" t="n">
-        <v>7128047</v>
+        <v>7128067</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7863,7 +7888,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack med nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7890,10 +7915,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120458603</v>
+        <v>120457474</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7906,27 +7931,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7935,13 +7960,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>514073</v>
+        <v>514114</v>
       </c>
       <c r="R66" t="n">
-        <v>7128124</v>
+        <v>7128116</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7971,11 +7996,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8002,10 +8022,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120457063</v>
+        <v>120457642</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>90972</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8018,39 +8038,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>514185</v>
+        <v>514115</v>
       </c>
       <c r="R67" t="n">
-        <v>7128134</v>
+        <v>7128095</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8083,11 +8093,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8114,10 +8119,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120457642</v>
+        <v>120458497</v>
       </c>
       <c r="B68" t="n">
-        <v>90972</v>
+        <v>57431</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8126,36 +8131,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6040186</v>
+        <v>103031</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>514115</v>
+        <v>514044</v>
       </c>
       <c r="R68" t="n">
-        <v>7128095</v>
+        <v>7128164</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8211,7 +8230,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120458790</v>
+        <v>120458603</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -8256,10 +8275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514077</v>
+        <v>514073</v>
       </c>
       <c r="R69" t="n">
-        <v>7128067</v>
+        <v>7128124</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8296,7 +8315,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack med nyligen intorkad kåda</t>
+          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8323,10 +8342,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120458497</v>
+        <v>120458309</v>
       </c>
       <c r="B70" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8335,50 +8354,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>514044</v>
+        <v>513941</v>
       </c>
       <c r="R70" t="n">
-        <v>7128164</v>
+        <v>7128278</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8434,7 +8444,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120457132</v>
+        <v>120461048</v>
       </c>
       <c r="B71" t="n">
         <v>57320</v>
@@ -8474,13 +8484,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>514162</v>
+        <v>514341</v>
       </c>
       <c r="R71" t="n">
-        <v>7128103</v>
+        <v>7127864</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8541,10 +8551,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120456942</v>
+        <v>120457160</v>
       </c>
       <c r="B72" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8557,21 +8567,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8581,13 +8591,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>514195</v>
+        <v>514165</v>
       </c>
       <c r="R72" t="n">
-        <v>7128135</v>
+        <v>7128093</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8617,11 +8627,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8648,10 +8653,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120461048</v>
+        <v>120460472</v>
       </c>
       <c r="B73" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8660,25 +8665,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8688,13 +8693,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>514341</v>
+        <v>514351</v>
       </c>
       <c r="R73" t="n">
-        <v>7127864</v>
+        <v>7127962</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8724,11 +8729,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8755,10 +8755,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120457160</v>
+        <v>120456991</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>514165</v>
+        <v>514191</v>
       </c>
       <c r="R74" t="n">
-        <v>7128093</v>
+        <v>7128149</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -6117,10 +6117,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120458528</v>
+        <v>120457746</v>
       </c>
       <c r="B49" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6129,25 +6129,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514056</v>
+        <v>514069</v>
       </c>
       <c r="R49" t="n">
-        <v>7128156</v>
+        <v>7128147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120457746</v>
+        <v>120458528</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514069</v>
+        <v>514056</v>
       </c>
       <c r="R50" t="n">
-        <v>7128147</v>
+        <v>7128156</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6321,10 +6321,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120457216</v>
+        <v>120456942</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514115</v>
+        <v>514195</v>
       </c>
       <c r="R51" t="n">
-        <v>7128119</v>
+        <v>7128135</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6397,6 +6397,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6423,7 +6428,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120456942</v>
+        <v>120457132</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -6463,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514195</v>
+        <v>514162</v>
       </c>
       <c r="R52" t="n">
-        <v>7128135</v>
+        <v>7128103</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6530,10 +6535,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120457132</v>
+        <v>120457216</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6546,21 +6551,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6570,10 +6575,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514162</v>
+        <v>514115</v>
       </c>
       <c r="R53" t="n">
-        <v>7128103</v>
+        <v>7128119</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6606,11 +6611,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -8119,10 +8119,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120458497</v>
+        <v>120458603</v>
       </c>
       <c r="B68" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8131,20 +8131,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8152,14 +8152,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8168,13 +8164,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>514044</v>
+        <v>514073</v>
       </c>
       <c r="R68" t="n">
-        <v>7128164</v>
+        <v>7128124</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8204,6 +8200,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8230,10 +8231,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120458603</v>
+        <v>120458497</v>
       </c>
       <c r="B69" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8242,20 +8243,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8263,10 +8264,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8275,13 +8280,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514073</v>
+        <v>514044</v>
       </c>
       <c r="R69" t="n">
-        <v>7128124</v>
+        <v>7128164</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8311,11 +8316,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -5796,10 +5796,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120457063</v>
+        <v>120456991</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5812,42 +5812,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514185</v>
+        <v>514191</v>
       </c>
       <c r="R46" t="n">
-        <v>7128134</v>
+        <v>7128149</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5877,11 +5872,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5908,10 +5898,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120460607</v>
+        <v>120457567</v>
       </c>
       <c r="B47" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5920,25 +5910,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5948,13 +5938,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514397</v>
+        <v>514117</v>
       </c>
       <c r="R47" t="n">
-        <v>7127995</v>
+        <v>7128094</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6010,7 +6000,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120458240</v>
+        <v>120459839</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -6050,13 +6040,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513929</v>
+        <v>514180</v>
       </c>
       <c r="R48" t="n">
-        <v>7128250</v>
+        <v>7128054</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6117,10 +6107,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120457746</v>
+        <v>120459113</v>
       </c>
       <c r="B49" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6133,21 +6123,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6157,13 +6147,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514069</v>
+        <v>514080</v>
       </c>
       <c r="R49" t="n">
-        <v>7128147</v>
+        <v>7128047</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6193,6 +6183,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6219,10 +6214,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120458528</v>
+        <v>120456942</v>
       </c>
       <c r="B50" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6231,25 +6226,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6259,13 +6254,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514056</v>
+        <v>514195</v>
       </c>
       <c r="R50" t="n">
-        <v>7128156</v>
+        <v>7128135</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6295,6 +6290,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6321,7 +6321,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120456942</v>
+        <v>120457729</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -6355,16 +6355,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514195</v>
+        <v>514077</v>
       </c>
       <c r="R51" t="n">
-        <v>7128135</v>
+        <v>7128136</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6401,7 +6406,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120457132</v>
+        <v>120458931</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6440,20 +6445,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6461,20 +6466,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514162</v>
+        <v>514084</v>
       </c>
       <c r="R52" t="n">
-        <v>7128103</v>
+        <v>7128053</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6504,11 +6513,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6535,10 +6539,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120457216</v>
+        <v>120459988</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6551,21 +6555,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6575,13 +6579,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514115</v>
+        <v>514236</v>
       </c>
       <c r="R53" t="n">
-        <v>7128119</v>
+        <v>7127956</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6637,7 +6641,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120460533</v>
+        <v>120457063</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6682,10 +6686,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514358</v>
+        <v>514185</v>
       </c>
       <c r="R54" t="n">
-        <v>7127980</v>
+        <v>7128134</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6722,7 +6726,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6749,10 +6753,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120459749</v>
+        <v>120460105</v>
       </c>
       <c r="B55" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6765,21 +6769,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6789,10 +6793,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514168</v>
+        <v>514241</v>
       </c>
       <c r="R55" t="n">
-        <v>7128051</v>
+        <v>7127904</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6825,6 +6829,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6851,10 +6860,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120459988</v>
+        <v>120460533</v>
       </c>
       <c r="B56" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6867,37 +6876,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514236</v>
+        <v>514358</v>
       </c>
       <c r="R56" t="n">
-        <v>7127956</v>
+        <v>7127980</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6927,6 +6941,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6953,10 +6972,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120458347</v>
+        <v>120457642</v>
       </c>
       <c r="B57" t="n">
-        <v>91146</v>
+        <v>90972</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6965,25 +6984,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>760</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6993,10 +7007,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513938</v>
+        <v>514115</v>
       </c>
       <c r="R57" t="n">
-        <v>7128279</v>
+        <v>7128095</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7055,10 +7069,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120458931</v>
+        <v>120459749</v>
       </c>
       <c r="B58" t="n">
-        <v>57431</v>
+        <v>90598</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7067,45 +7081,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>514084</v>
+        <v>514168</v>
       </c>
       <c r="R58" t="n">
-        <v>7128053</v>
+        <v>7128051</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7161,10 +7171,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120457678</v>
+        <v>120457474</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7177,37 +7187,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>514096</v>
+        <v>514114</v>
       </c>
       <c r="R59" t="n">
-        <v>7128129</v>
+        <v>7128116</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7237,11 +7252,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7268,10 +7278,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120459113</v>
+        <v>120458309</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7284,21 +7294,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7308,10 +7318,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>514080</v>
+        <v>513941</v>
       </c>
       <c r="R60" t="n">
-        <v>7128047</v>
+        <v>7128278</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7344,11 +7354,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7375,7 +7380,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120459839</v>
+        <v>120457678</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -7415,10 +7420,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>514180</v>
+        <v>514096</v>
       </c>
       <c r="R61" t="n">
-        <v>7128054</v>
+        <v>7128129</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7482,7 +7487,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120457729</v>
+        <v>120457132</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7516,21 +7521,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>514077</v>
+        <v>514162</v>
       </c>
       <c r="R62" t="n">
-        <v>7128136</v>
+        <v>7128103</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7594,10 +7594,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120457567</v>
+        <v>120458347</v>
       </c>
       <c r="B63" t="n">
-        <v>90598</v>
+        <v>91146</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7606,25 +7606,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>514117</v>
+        <v>513938</v>
       </c>
       <c r="R63" t="n">
-        <v>7128094</v>
+        <v>7128279</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120460105</v>
+        <v>120458790</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7730,16 +7730,21 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>514241</v>
+        <v>514077</v>
       </c>
       <c r="R64" t="n">
-        <v>7127904</v>
+        <v>7128067</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7776,7 +7781,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack med nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7803,7 +7808,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120458790</v>
+        <v>120458240</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7837,21 +7842,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>514077</v>
+        <v>513929</v>
       </c>
       <c r="R65" t="n">
-        <v>7128067</v>
+        <v>7128250</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack med nyligen intorkad kåda</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7915,10 +7915,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120457474</v>
+        <v>120457216</v>
       </c>
       <c r="B66" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7931,42 +7931,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>514114</v>
+        <v>514115</v>
       </c>
       <c r="R66" t="n">
-        <v>7128116</v>
+        <v>7128119</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8022,10 +8017,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120457642</v>
+        <v>120457160</v>
       </c>
       <c r="B67" t="n">
-        <v>90972</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8038,16 +8033,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8057,13 +8057,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>514115</v>
+        <v>514165</v>
       </c>
       <c r="R67" t="n">
-        <v>7128095</v>
+        <v>7128093</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8119,10 +8119,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120458603</v>
+        <v>120460607</v>
       </c>
       <c r="B68" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8131,46 +8131,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>514073</v>
+        <v>514397</v>
       </c>
       <c r="R68" t="n">
-        <v>7128124</v>
+        <v>7127995</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8200,11 +8195,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8231,10 +8221,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120458497</v>
+        <v>120461048</v>
       </c>
       <c r="B69" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8243,20 +8233,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8264,29 +8254,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514044</v>
+        <v>514341</v>
       </c>
       <c r="R69" t="n">
-        <v>7128164</v>
+        <v>7127864</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8316,6 +8297,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8342,10 +8328,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120458309</v>
+        <v>120458528</v>
       </c>
       <c r="B70" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8354,25 +8340,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8382,13 +8368,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513941</v>
+        <v>514056</v>
       </c>
       <c r="R70" t="n">
-        <v>7128278</v>
+        <v>7128156</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8444,10 +8430,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120461048</v>
+        <v>120460472</v>
       </c>
       <c r="B71" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8456,25 +8442,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8484,13 +8470,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>514341</v>
+        <v>514351</v>
       </c>
       <c r="R71" t="n">
-        <v>7127864</v>
+        <v>7127962</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8520,11 +8506,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8551,10 +8532,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120457160</v>
+        <v>120457746</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8567,21 +8548,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8591,10 +8572,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>514165</v>
+        <v>514069</v>
       </c>
       <c r="R72" t="n">
-        <v>7128093</v>
+        <v>7128147</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8653,10 +8634,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120460472</v>
+        <v>120458603</v>
       </c>
       <c r="B73" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8665,38 +8646,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>514351</v>
+        <v>514073</v>
       </c>
       <c r="R73" t="n">
-        <v>7127962</v>
+        <v>7128124</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8729,6 +8715,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8755,10 +8746,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120456991</v>
+        <v>120458497</v>
       </c>
       <c r="B74" t="n">
-        <v>78278</v>
+        <v>57431</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8767,41 +8758,50 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>514191</v>
+        <v>514044</v>
       </c>
       <c r="R74" t="n">
-        <v>7128149</v>
+        <v>7128164</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -5796,10 +5796,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120456991</v>
+        <v>120460607</v>
       </c>
       <c r="B46" t="n">
-        <v>78278</v>
+        <v>96885</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5808,25 +5808,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514191</v>
+        <v>514397</v>
       </c>
       <c r="R46" t="n">
-        <v>7128149</v>
+        <v>7127995</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120457567</v>
+        <v>120458309</v>
       </c>
       <c r="B47" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5914,21 +5914,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514117</v>
+        <v>513941</v>
       </c>
       <c r="R47" t="n">
-        <v>7128094</v>
+        <v>7128278</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6000,10 +6000,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120459839</v>
+        <v>120460472</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6012,25 +6012,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6040,13 +6040,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514180</v>
+        <v>514351</v>
       </c>
       <c r="R48" t="n">
-        <v>7128054</v>
+        <v>7127962</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6076,11 +6076,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6107,7 +6102,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120459113</v>
+        <v>120457678</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -6147,13 +6142,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514080</v>
+        <v>514096</v>
       </c>
       <c r="R49" t="n">
-        <v>7128047</v>
+        <v>7128129</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6214,10 +6209,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120456942</v>
+        <v>120457216</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6230,21 +6225,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6254,10 +6249,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514195</v>
+        <v>514115</v>
       </c>
       <c r="R50" t="n">
-        <v>7128135</v>
+        <v>7128119</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6290,11 +6285,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6321,10 +6311,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120457729</v>
+        <v>120458347</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>91146</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6333,43 +6323,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514077</v>
+        <v>513938</v>
       </c>
       <c r="R51" t="n">
-        <v>7128136</v>
+        <v>7128279</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6402,11 +6387,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6433,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120458931</v>
+        <v>120457729</v>
       </c>
       <c r="B52" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6445,20 +6425,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6466,9 +6446,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6477,13 +6458,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514084</v>
+        <v>514077</v>
       </c>
       <c r="R52" t="n">
-        <v>7128053</v>
+        <v>7128136</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6513,6 +6494,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6539,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120459988</v>
+        <v>120457567</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6555,21 +6541,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6579,13 +6565,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514236</v>
+        <v>514117</v>
       </c>
       <c r="R53" t="n">
-        <v>7127956</v>
+        <v>7128094</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6641,7 +6627,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120457063</v>
+        <v>120460105</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6675,21 +6661,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514185</v>
+        <v>514241</v>
       </c>
       <c r="R54" t="n">
-        <v>7128134</v>
+        <v>7127904</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6726,7 +6707,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6753,7 +6734,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120460105</v>
+        <v>120458603</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6787,16 +6768,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514241</v>
+        <v>514073</v>
       </c>
       <c r="R55" t="n">
-        <v>7127904</v>
+        <v>7128124</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6833,7 +6819,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6860,7 +6846,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120460533</v>
+        <v>120457132</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6894,21 +6880,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514358</v>
+        <v>514162</v>
       </c>
       <c r="R56" t="n">
-        <v>7127980</v>
+        <v>7128103</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6945,7 +6926,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6972,10 +6953,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120457642</v>
+        <v>120459749</v>
       </c>
       <c r="B57" t="n">
-        <v>90972</v>
+        <v>90598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6988,16 +6969,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7007,10 +6993,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>514115</v>
+        <v>514168</v>
       </c>
       <c r="R57" t="n">
-        <v>7128095</v>
+        <v>7128051</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7069,10 +7055,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120459749</v>
+        <v>120458497</v>
       </c>
       <c r="B58" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7081,41 +7067,50 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>514168</v>
+        <v>514044</v>
       </c>
       <c r="R58" t="n">
-        <v>7128051</v>
+        <v>7128164</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7171,10 +7166,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120457474</v>
+        <v>120457642</v>
       </c>
       <c r="B59" t="n">
-        <v>57473</v>
+        <v>90972</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7187,42 +7182,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>514114</v>
+        <v>514115</v>
       </c>
       <c r="R59" t="n">
-        <v>7128116</v>
+        <v>7128095</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7278,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120458309</v>
+        <v>120457063</v>
       </c>
       <c r="B60" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7294,34 +7279,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513941</v>
+        <v>514185</v>
       </c>
       <c r="R60" t="n">
-        <v>7128278</v>
+        <v>7128134</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7354,6 +7344,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7380,10 +7375,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120457678</v>
+        <v>120457746</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7396,21 +7391,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7420,10 +7415,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>514096</v>
+        <v>514069</v>
       </c>
       <c r="R61" t="n">
-        <v>7128129</v>
+        <v>7128147</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7456,11 +7451,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7487,10 +7477,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120457132</v>
+        <v>120459988</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7503,21 +7493,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7527,13 +7517,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>514162</v>
+        <v>514236</v>
       </c>
       <c r="R62" t="n">
-        <v>7128103</v>
+        <v>7127956</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7563,11 +7553,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7594,10 +7579,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120458347</v>
+        <v>120459839</v>
       </c>
       <c r="B63" t="n">
-        <v>91146</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7606,25 +7591,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7634,13 +7619,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513938</v>
+        <v>514180</v>
       </c>
       <c r="R63" t="n">
-        <v>7128279</v>
+        <v>7128054</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7670,6 +7655,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7696,7 +7686,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120458790</v>
+        <v>120458240</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7730,21 +7720,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>514077</v>
+        <v>513929</v>
       </c>
       <c r="R64" t="n">
-        <v>7128067</v>
+        <v>7128250</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7781,7 +7766,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack med nyligen intorkad kåda</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7808,7 +7793,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120458240</v>
+        <v>120458790</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7842,16 +7827,21 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513929</v>
+        <v>514077</v>
       </c>
       <c r="R65" t="n">
-        <v>7128250</v>
+        <v>7128067</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7888,7 +7878,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack med nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7915,10 +7905,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120457216</v>
+        <v>120457474</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7931,37 +7921,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>514115</v>
+        <v>514114</v>
       </c>
       <c r="R66" t="n">
-        <v>7128119</v>
+        <v>7128116</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8017,10 +8012,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120457160</v>
+        <v>120456991</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8033,21 +8028,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8057,10 +8052,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>514165</v>
+        <v>514191</v>
       </c>
       <c r="R67" t="n">
-        <v>7128093</v>
+        <v>7128149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8119,10 +8114,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120460607</v>
+        <v>120460533</v>
       </c>
       <c r="B68" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8131,41 +8126,46 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>514397</v>
+        <v>514358</v>
       </c>
       <c r="R68" t="n">
-        <v>7127995</v>
+        <v>7127980</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8195,6 +8195,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8221,7 +8226,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120461048</v>
+        <v>120456942</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -8261,13 +8266,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514341</v>
+        <v>514195</v>
       </c>
       <c r="R69" t="n">
-        <v>7127864</v>
+        <v>7128135</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8328,10 +8333,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120458528</v>
+        <v>120457160</v>
       </c>
       <c r="B70" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8340,25 +8345,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8368,10 +8373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>514056</v>
+        <v>514165</v>
       </c>
       <c r="R70" t="n">
-        <v>7128156</v>
+        <v>7128093</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8430,10 +8435,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120460472</v>
+        <v>120459113</v>
       </c>
       <c r="B71" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8442,25 +8447,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8470,10 +8475,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>514351</v>
+        <v>514080</v>
       </c>
       <c r="R71" t="n">
-        <v>7127962</v>
+        <v>7128047</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8506,6 +8511,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8532,10 +8542,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120457746</v>
+        <v>120461048</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8548,21 +8558,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8572,10 +8582,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>514069</v>
+        <v>514341</v>
       </c>
       <c r="R72" t="n">
-        <v>7128147</v>
+        <v>7127864</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8608,6 +8618,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8634,10 +8649,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120458603</v>
+        <v>120458931</v>
       </c>
       <c r="B73" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8646,20 +8661,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8667,10 +8682,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8679,13 +8693,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>514073</v>
+        <v>514084</v>
       </c>
       <c r="R73" t="n">
-        <v>7128124</v>
+        <v>7128053</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8715,11 +8729,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8746,10 +8755,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120458497</v>
+        <v>120458528</v>
       </c>
       <c r="B74" t="n">
-        <v>57431</v>
+        <v>96885</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8762,46 +8771,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>514044</v>
+        <v>514056</v>
       </c>
       <c r="R74" t="n">
-        <v>7128164</v>
+        <v>7128156</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -8758,7 +8758,7 @@
         <v>120458347</v>
       </c>
       <c r="B74" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -8758,7 +8758,7 @@
         <v>120458347</v>
       </c>
       <c r="B74" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2020 artfynd.xlsx
+++ b/artfynd/A 36809-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88782527</v>
+        <v>89594756</v>
       </c>
       <c r="B7" t="n">
         <v>56395</v>
@@ -1290,23 +1290,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514238.5182067568</v>
+        <v>514238.9511901711</v>
       </c>
       <c r="R7" t="n">
-        <v>7128161.549234214</v>
+        <v>7128161.985686115</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,14 +1366,18 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88782509</v>
+        <v>89594754</v>
       </c>
       <c r="B8" t="n">
         <v>78570</v>
@@ -1411,22 +1411,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514200.9783977771</v>
+        <v>514200.9804011364</v>
       </c>
       <c r="R8" t="n">
-        <v>7128095.338797636</v>
+        <v>7128094.904347612</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,9 +1471,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1486,14 +1487,18 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88782532</v>
+        <v>89594755</v>
       </c>
       <c r="B9" t="n">
         <v>78503</v>
@@ -1527,22 +1532,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514228.184776813</v>
+        <v>514228.1827696093</v>
       </c>
       <c r="R9" t="n">
-        <v>7128138.475540235</v>
+        <v>7128138.909984135</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,9 +1592,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1602,10 +1608,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2779,10 +2789,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89594756</v>
+        <v>89594746</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
+        <v>78596</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,25 +2801,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2819,10 +2829,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514238.9511901711</v>
+        <v>514226.0248175223</v>
       </c>
       <c r="R20" t="n">
-        <v>7128161.985686115</v>
+        <v>7127946.865754246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2865,11 +2875,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,10 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89594755</v>
+        <v>89594747</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>78602</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,21 +2921,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2940,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514228.1827696093</v>
+        <v>514226.0248175223</v>
       </c>
       <c r="R21" t="n">
-        <v>7128138.909984135</v>
+        <v>7127946.865754246</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2996,11 +3001,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89594754</v>
+        <v>96276200</v>
       </c>
       <c r="B22" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3037,37 +3037,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514200.9804011364</v>
+        <v>514078.2046952047</v>
       </c>
       <c r="R22" t="n">
-        <v>7128094.904347612</v>
+        <v>7128117.366896777</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3091,7 +3094,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3101,7 +3104,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3109,6 +3112,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, relativt färska</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3117,11 +3125,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3131,21 +3134,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89594746</v>
+        <v>96276906</v>
       </c>
       <c r="B23" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3154,41 +3153,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514226.0248175223</v>
+        <v>514212.511051541</v>
       </c>
       <c r="R23" t="n">
-        <v>7127946.865754246</v>
+        <v>7127952.88607844</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3247,21 +3247,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89594747</v>
+        <v>96277250</v>
       </c>
       <c r="B24" t="n">
-        <v>78602</v>
+        <v>78569</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3270,41 +3266,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514226.0248175223</v>
+        <v>514226.4538191929</v>
       </c>
       <c r="R24" t="n">
-        <v>7127946.865754246</v>
+        <v>7127948.1711761</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3328,7 +3325,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3338,7 +3335,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3363,18 +3360,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96276200</v>
+        <v>96276767</v>
       </c>
       <c r="B25" t="n">
         <v>56395</v>
@@ -3417,10 +3410,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514078.2046952047</v>
+        <v>514128.2050770036</v>
       </c>
       <c r="R25" t="n">
-        <v>7128117.366896777</v>
+        <v>7128028.09664302</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3467,7 +3460,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, relativt färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,10 +3487,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96276906</v>
+        <v>96277801</v>
       </c>
       <c r="B26" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3510,35 +3503,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514212.511051541</v>
+        <v>514222.9287156384</v>
       </c>
       <c r="R26" t="n">
-        <v>7127952.88607844</v>
+        <v>7128146.271408552</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3581,6 +3576,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3607,10 +3607,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96277250</v>
+        <v>96272964</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
+        <v>89952</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514226.4538191929</v>
+        <v>513943.4973630594</v>
       </c>
       <c r="R27" t="n">
-        <v>7127948.1711761</v>
+        <v>7128277.498519013</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3720,10 +3720,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96276767</v>
+        <v>96272965</v>
       </c>
       <c r="B28" t="n">
-        <v>56395</v>
+        <v>78570</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3736,37 +3736,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514128.2050770036</v>
+        <v>513943.4973630594</v>
       </c>
       <c r="R28" t="n">
-        <v>7128028.09664302</v>
+        <v>7128277.498519013</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3809,11 +3807,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3840,10 +3833,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96277801</v>
+        <v>96277025</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
+        <v>78602</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3852,41 +3845,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514222.9287156384</v>
+        <v>514234.0841323133</v>
       </c>
       <c r="R29" t="n">
-        <v>7128146.271408552</v>
+        <v>7127897.371855048</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3929,11 +3920,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3960,10 +3946,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96272964</v>
+        <v>96277282</v>
       </c>
       <c r="B30" t="n">
-        <v>89952</v>
+        <v>78570</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3972,25 +3958,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4001,10 +3987,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513943.4973630594</v>
+        <v>514226.4538191929</v>
       </c>
       <c r="R30" t="n">
-        <v>7128277.498519013</v>
+        <v>7127948.1711761</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4073,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96272965</v>
+        <v>96276837</v>
       </c>
       <c r="B31" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4089,35 +4075,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513943.4973630594</v>
+        <v>514142.5604390417</v>
       </c>
       <c r="R31" t="n">
-        <v>7128277.498519013</v>
+        <v>7128028.162531699</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4160,6 +4148,11 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4186,10 +4179,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96277025</v>
+        <v>96272968</v>
       </c>
       <c r="B32" t="n">
-        <v>78602</v>
+        <v>78603</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4202,21 +4195,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4227,10 +4220,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514234.0841323133</v>
+        <v>513943.4973630594</v>
       </c>
       <c r="R32" t="n">
-        <v>7127897.371855048</v>
+        <v>7128277.498519013</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4299,10 +4292,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96277282</v>
+        <v>96277464</v>
       </c>
       <c r="B33" t="n">
-        <v>78570</v>
+        <v>78603</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4311,25 +4304,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4340,10 +4333,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514226.4538191929</v>
+        <v>514255.8221578836</v>
       </c>
       <c r="R33" t="n">
-        <v>7127948.1711761</v>
+        <v>7127994.361512901</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4412,10 +4405,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96276837</v>
+        <v>96276289</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
+        <v>78596</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4424,41 +4417,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514142.5604390417</v>
+        <v>514084.9959255125</v>
       </c>
       <c r="R34" t="n">
-        <v>7128028.162531699</v>
+        <v>7128059.18030185</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4501,11 +4492,6 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4532,10 +4518,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96272968</v>
+        <v>96277002</v>
       </c>
       <c r="B35" t="n">
-        <v>78603</v>
+        <v>78570</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4544,25 +4530,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4573,10 +4559,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513943.4973630594</v>
+        <v>514234.0841323133</v>
       </c>
       <c r="R35" t="n">
-        <v>7128277.498519013</v>
+        <v>7127897.371855048</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4645,10 +4631,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96277464</v>
+        <v>96277470</v>
       </c>
       <c r="B36" t="n">
-        <v>78603</v>
+        <v>78570</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4657,25 +4643,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4758,10 +4744,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96276289</v>
+        <v>96277462</v>
       </c>
       <c r="B37" t="n">
-        <v>78596</v>
+        <v>78569</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4770,25 +4756,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4799,10 +4785,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514084.9959255125</v>
+        <v>514255.8221578836</v>
       </c>
       <c r="R37" t="n">
-        <v>7128059.18030185</v>
+        <v>7127994.361512901</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4871,10 +4857,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96277002</v>
+        <v>96277035</v>
       </c>
       <c r="B38" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4887,35 +4873,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514234.0841323133</v>
+        <v>514234.0981883124</v>
       </c>
       <c r="R38" t="n">
-        <v>7127897.371855048</v>
+        <v>7127894.330508536</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4958,6 +4946,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4984,10 +4977,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96277470</v>
+        <v>96277639</v>
       </c>
       <c r="B39" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5000,35 +4993,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514255.8221578836</v>
+        <v>514204.4383711794</v>
       </c>
       <c r="R39" t="n">
-        <v>7127994.361512901</v>
+        <v>7128099.699343724</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5071,6 +5066,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5097,10 +5097,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96277462</v>
+        <v>96277147</v>
       </c>
       <c r="B40" t="n">
-        <v>78569</v>
+        <v>56395</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5113,35 +5113,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514255.8221578836</v>
+        <v>514253.2395030356</v>
       </c>
       <c r="R40" t="n">
-        <v>7127994.361512901</v>
+        <v>7127894.419032215</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5184,6 +5186,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5210,10 +5217,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96277035</v>
+        <v>96272967</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
+        <v>78569</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5226,37 +5233,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514234.0981883124</v>
+        <v>513943.4973630594</v>
       </c>
       <c r="R41" t="n">
-        <v>7127894.330508536</v>
+        <v>7128277.498519013</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5299,11 +5304,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5330,10 +5330,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96277639</v>
+        <v>96276949</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
+        <v>78569</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5346,37 +5346,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514204.4383711794</v>
+        <v>514201.8518829145</v>
       </c>
       <c r="R42" t="n">
-        <v>7128099.699343724</v>
+        <v>7127905.912787987</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5419,11 +5417,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5450,10 +5443,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96277147</v>
+        <v>120459988</v>
       </c>
       <c r="B43" t="n">
-        <v>56395</v>
+        <v>79671</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5466,40 +5459,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514253.2395030356</v>
+        <v>514236</v>
       </c>
       <c r="R43" t="n">
-        <v>7127894.419032215</v>
+        <v>7127956</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5523,27 +5513,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5570,10 +5545,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>96272967</v>
+        <v>120460472</v>
       </c>
       <c r="B44" t="n">
-        <v>78569</v>
+        <v>91978</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5582,42 +5557,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513943.4973630594</v>
+        <v>514351</v>
       </c>
       <c r="R44" t="n">
-        <v>7128277.498519013</v>
+        <v>7127962</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5641,22 +5615,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5683,10 +5647,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>96276949</v>
+        <v>120459839</v>
       </c>
       <c r="B45" t="n">
-        <v>78569</v>
+        <v>57344</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5699,38 +5663,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514201.8518829145</v>
+        <v>514180</v>
       </c>
       <c r="R45" t="n">
-        <v>7127905.912787987</v>
+        <v>7128054</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5754,22 +5717,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5796,10 +5754,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120459988</v>
+        <v>120457678</v>
       </c>
       <c r="B46" t="n">
-        <v>79671</v>
+        <v>57344</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5812,21 +5770,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5836,10 +5794,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514236</v>
+        <v>514096</v>
       </c>
       <c r="R46" t="n">
-        <v>7127956</v>
+        <v>7128129</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5872,6 +5830,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5898,10 +5861,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120460472</v>
+        <v>120457729</v>
       </c>
       <c r="B47" t="n">
-        <v>91978</v>
+        <v>57344</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5910,38 +5873,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514351</v>
+        <v>514077</v>
       </c>
       <c r="R47" t="n">
-        <v>7127962</v>
+        <v>7128136</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5974,6 +5942,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6000,7 +5973,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120459839</v>
+        <v>120459113</v>
       </c>
       <c r="B48" t="n">
         <v>57344</v>
@@ -6040,13 +6013,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514180</v>
+        <v>514080</v>
       </c>
       <c r="R48" t="n">
-        <v>7128054</v>
+        <v>7128047</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6107,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120457678</v>
+        <v>120460607</v>
       </c>
       <c r="B49" t="n">
-        <v>57344</v>
+        <v>96994</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6119,25 +6092,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6147,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514096</v>
+        <v>514397</v>
       </c>
       <c r="R49" t="n">
-        <v>7128129</v>
+        <v>7127995</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6183,11 +6156,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6214,7 +6182,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120457729</v>
+        <v>120460533</v>
       </c>
       <c r="B50" t="n">
         <v>57344</v>
@@ -6259,10 +6227,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514077</v>
+        <v>514358</v>
       </c>
       <c r="R50" t="n">
-        <v>7128136</v>
+        <v>7127980</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6326,10 +6294,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120459113</v>
+        <v>120458931</v>
       </c>
       <c r="B51" t="n">
-        <v>57344</v>
+        <v>57455</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6338,20 +6306,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6359,20 +6327,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514080</v>
+        <v>514084</v>
       </c>
       <c r="R51" t="n">
-        <v>7128047</v>
+        <v>7128053</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6402,11 +6374,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6433,10 +6400,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120460607</v>
+        <v>120457642</v>
       </c>
       <c r="B52" t="n">
-        <v>96994</v>
+        <v>91066</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6445,25 +6412,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6473,13 +6435,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514397</v>
+        <v>514115</v>
       </c>
       <c r="R52" t="n">
-        <v>7127995</v>
+        <v>7128095</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6535,10 +6497,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120460533</v>
+        <v>120456991</v>
       </c>
       <c r="B53" t="n">
-        <v>57344</v>
+        <v>78326</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6551,42 +6513,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514358</v>
+        <v>514191</v>
       </c>
       <c r="R53" t="n">
-        <v>7127980</v>
+        <v>7128149</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6616,11 +6573,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6647,7 +6599,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120458931</v>
+        <v>120458497</v>
       </c>
       <c r="B54" t="n">
         <v>57455</v>
@@ -6682,7 +6634,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6691,10 +6648,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514084</v>
+        <v>514044</v>
       </c>
       <c r="R54" t="n">
-        <v>7128053</v>
+        <v>7128164</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6753,10 +6710,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120457642</v>
+        <v>120457474</v>
       </c>
       <c r="B55" t="n">
-        <v>91066</v>
+        <v>57497</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6769,32 +6726,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040186</v>
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514115</v>
+        <v>514114</v>
       </c>
       <c r="R55" t="n">
-        <v>7128095</v>
+        <v>7128116</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6850,10 +6817,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120456991</v>
+        <v>120457160</v>
       </c>
       <c r="B56" t="n">
-        <v>78326</v>
+        <v>78590</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6866,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6890,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514191</v>
+        <v>514165</v>
       </c>
       <c r="R56" t="n">
-        <v>7128149</v>
+        <v>7128093</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6952,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120458497</v>
+        <v>120461048</v>
       </c>
       <c r="B57" t="n">
-        <v>57455</v>
+        <v>57344</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6964,20 +6931,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6985,29 +6952,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>514044</v>
+        <v>514341</v>
       </c>
       <c r="R57" t="n">
-        <v>7128164</v>
+        <v>7127864</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7037,6 +6995,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7063,10 +7026,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120457474</v>
+        <v>120458603</v>
       </c>
       <c r="B58" t="n">
-        <v>57497</v>
+        <v>57344</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7079,27 +7042,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7108,13 +7071,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>514114</v>
+        <v>514073</v>
       </c>
       <c r="R58" t="n">
-        <v>7128116</v>
+        <v>7128124</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7144,6 +7107,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7170,10 +7138,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120457160</v>
+        <v>120458790</v>
       </c>
       <c r="B59" t="n">
-        <v>78590</v>
+        <v>57344</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7186,37 +7154,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>514165</v>
+        <v>514077</v>
       </c>
       <c r="R59" t="n">
-        <v>7128093</v>
+        <v>7128067</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7246,6 +7219,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack med nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7272,7 +7250,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120461048</v>
+        <v>120456942</v>
       </c>
       <c r="B60" t="n">
         <v>57344</v>
@@ -7312,13 +7290,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>514341</v>
+        <v>514195</v>
       </c>
       <c r="R60" t="n">
-        <v>7127864</v>
+        <v>7128135</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7379,10 +7357,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120458603</v>
+        <v>120458309</v>
       </c>
       <c r="B61" t="n">
-        <v>57344</v>
+        <v>79671</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7395,39 +7373,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>514073</v>
+        <v>513941</v>
       </c>
       <c r="R61" t="n">
-        <v>7128124</v>
+        <v>7128278</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7460,11 +7433,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Kåda har runnit över snitselbandet.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7491,10 +7459,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120458790</v>
+        <v>120457567</v>
       </c>
       <c r="B62" t="n">
-        <v>57344</v>
+        <v>90688</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7507,39 +7475,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>514077</v>
+        <v>514117</v>
       </c>
       <c r="R62" t="n">
-        <v>7128067</v>
+        <v>7128094</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7572,11 +7535,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack med nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7603,10 +7561,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120456942</v>
+        <v>120457746</v>
       </c>
       <c r="B63" t="n">
-        <v>57344</v>
+        <v>90670</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7619,21 +7577,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7643,13 +7601,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>514195</v>
+        <v>514069</v>
       </c>
       <c r="R63" t="n">
-        <v>7128135</v>
+        <v>7128147</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7679,11 +7637,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7710,10 +7663,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120458309</v>
+        <v>120458240</v>
       </c>
       <c r="B64" t="n">
-        <v>79671</v>
+        <v>57344</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7726,21 +7679,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7750,10 +7703,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513941</v>
+        <v>513929</v>
       </c>
       <c r="R64" t="n">
-        <v>7128278</v>
+        <v>7128250</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7786,6 +7739,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7812,10 +7770,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120457567</v>
+        <v>120457216</v>
       </c>
       <c r="B65" t="n">
-        <v>90688</v>
+        <v>90670</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7828,21 +7786,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7852,10 +7810,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>514117</v>
+        <v>514115</v>
       </c>
       <c r="R65" t="n">
-        <v>7128094</v>
+        <v>7128119</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7914,10 +7872,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120457746</v>
+        <v>120459749</v>
       </c>
       <c r="B66" t="n">
-        <v>90670</v>
+        <v>90688</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7930,21 +7888,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7954,13 +7912,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>514069</v>
+        <v>514168</v>
       </c>
       <c r="R66" t="n">
-        <v>7128147</v>
+        <v>7128051</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8016,7 +7974,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120458240</v>
+        <v>120460105</v>
       </c>
       <c r="B67" t="n">
         <v>57344</v>
@@ -8056,10 +8014,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513929</v>
+        <v>514241</v>
       </c>
       <c r="R67" t="n">
-        <v>7128250</v>
+        <v>7127904</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8123,10 +8081,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120457216</v>
+        <v>120457132</v>
       </c>
       <c r="B68" t="n">
-        <v>90670</v>
+        <v>57344</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8139,21 +8097,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8163,10 +8121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>514115</v>
+        <v>514162</v>
       </c>
       <c r="R68" t="n">
-        <v>7128119</v>
+        <v>7128103</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8199,6 +8157,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8225,10 +8188,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120459749</v>
+        <v>120457063</v>
       </c>
       <c r="B69" t="n">
-        <v>90688</v>
+        <v>57344</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8241,34 +8204,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514168</v>
+        <v>514185</v>
       </c>
       <c r="R69" t="n">
-        <v>7128051</v>
+        <v>7128134</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8301,6 +8269,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Nyligen intorkad kåda</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8327,10 +8300,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120460105</v>
+        <v>120458528</v>
       </c>
       <c r="B70" t="n">
-        <v>57344</v>
+        <v>96994</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8339,25 +8312,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8367,13 +8340,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>514241</v>
+        <v>514056</v>
       </c>
       <c r="R70" t="n">
-        <v>7127904</v>
+        <v>7128156</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8403,11 +8376,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8434,37 +8402,37 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120457132</v>
+        <v>120458347</v>
       </c>
       <c r="B71" t="n">
-        <v>57344</v>
+        <v>91271</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8474,10 +8442,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>514162</v>
+        <v>513938</v>
       </c>
       <c r="R71" t="n">
-        <v>7128103</v>
+        <v>7128279</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8512,11 +8480,6 @@
           <t>2024-10-17</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8538,322 +8501,6 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>120457063</v>
-      </c>
-      <c r="B72" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Strömsund, Strömsund, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>514185</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7128134</v>
-      </c>
-      <c r="S72" t="n">
-        <v>15</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack. Nyligen intorkad kåda</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>120458528</v>
-      </c>
-      <c r="B73" t="n">
-        <v>96994</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Strömsund, Strömsund, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>514056</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7128156</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>120458347</v>
-      </c>
-      <c r="B74" t="n">
-        <v>91271</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>760</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Haploporus odorus</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Strömsund, Strömsund, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>513938</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7128279</v>
-      </c>
-      <c r="S74" t="n">
-        <v>15</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
